--- a/excel/Kommune_CFO_Executive_Konsern_2026.xlsx
+++ b/excel/Kommune_CFO_Executive_Konsern_2026.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 34b26c24bda8ebb32ac3bbfaabd0d5fe5ff9b885ff5d9a067ed58b83d7d069ff</t>
+          <t>SHA-256: 040342b04348696cde54ec73aed9e84aa5d245e22964c05553f442ac82f441da</t>
         </is>
       </c>
     </row>
